--- a/lai/valuationquan/AIinduindex.xlsx
+++ b/lai/valuationquan/AIinduindex.xlsx
@@ -413,7 +413,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K2259"/>
+  <dimension ref="A1:K2282"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
@@ -82475,7 +82475,7 @@
         <v>361445000000</v>
       </c>
       <c r="I2131">
-        <f t="shared" ref="I2131:I2259" si="91">I2130+1</f>
+        <f t="shared" ref="I2131:I2282" si="91">I2130+1</f>
         <v>2129</v>
       </c>
       <c r="J2131">
@@ -84259,7 +84259,7 @@
         <v>2087.19</v>
       </c>
       <c r="F2177">
-        <f t="shared" ref="F2177:F2259" si="94">E2177/1000</f>
+        <f t="shared" ref="F2177:F2282" si="94">E2177/1000</f>
         <v>2.0871900000000001</v>
       </c>
       <c r="G2177">
@@ -86383,7 +86383,7 @@
         <v>1.1668063974876615</v>
       </c>
       <c r="K2231">
-        <f t="shared" ref="K2231:K2259" si="95">SUM(F1982:F2231)/250</f>
+        <f t="shared" ref="K2231:K2282" si="95">SUM(F1982:F2231)/250</f>
         <v>1.8407580399999994</v>
       </c>
     </row>
@@ -87477,6 +87477,903 @@
       <c r="K2259">
         <f t="shared" si="95"/>
         <v>1.8694703600000002</v>
+      </c>
+    </row>
+    <row r="2260" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2260" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B2260">
+        <v>1725.32</v>
+      </c>
+      <c r="C2260">
+        <v>1773.25</v>
+      </c>
+      <c r="D2260">
+        <v>1724.39</v>
+      </c>
+      <c r="E2260">
+        <v>1759.97</v>
+      </c>
+      <c r="F2260">
+        <f t="shared" si="94"/>
+        <v>1.75997</v>
+      </c>
+      <c r="G2260">
+        <v>329416875</v>
+      </c>
+      <c r="H2260" s="3">
+        <v>715089000000</v>
+      </c>
+      <c r="I2260">
+        <f t="shared" si="91"/>
+        <v>2258</v>
+      </c>
+      <c r="J2260">
+        <f>SUM($F$3:F2260)/I2260</f>
+        <v>1.175057254207261</v>
+      </c>
+      <c r="K2260">
+        <f t="shared" si="95"/>
+        <v>1.8703061600000004</v>
+      </c>
+    </row>
+    <row r="2261" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2261" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B2261">
+        <v>1750.16</v>
+      </c>
+      <c r="C2261">
+        <v>1778.91</v>
+      </c>
+      <c r="D2261">
+        <v>1734.39</v>
+      </c>
+      <c r="E2261">
+        <v>1738.17</v>
+      </c>
+      <c r="F2261">
+        <f t="shared" si="94"/>
+        <v>1.73817</v>
+      </c>
+      <c r="G2261">
+        <v>328095249</v>
+      </c>
+      <c r="H2261" s="3">
+        <v>665541000000</v>
+      </c>
+      <c r="I2261">
+        <f t="shared" si="91"/>
+        <v>2259</v>
+      </c>
+      <c r="J2261">
+        <f>SUM($F$3:F2261)/I2261</f>
+        <v>1.1753065294378024</v>
+      </c>
+      <c r="K2261">
+        <f t="shared" si="95"/>
+        <v>1.8711626800000003</v>
+      </c>
+    </row>
+    <row r="2262" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2262" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B2262">
+        <v>1742.61</v>
+      </c>
+      <c r="C2262">
+        <v>1769.18</v>
+      </c>
+      <c r="D2262">
+        <v>1740.91</v>
+      </c>
+      <c r="E2262">
+        <v>1756.72</v>
+      </c>
+      <c r="F2262">
+        <f t="shared" si="94"/>
+        <v>1.7567200000000001</v>
+      </c>
+      <c r="G2262">
+        <v>288795548</v>
+      </c>
+      <c r="H2262" s="3">
+        <v>590827000000</v>
+      </c>
+      <c r="I2262">
+        <f t="shared" si="91"/>
+        <v>2260</v>
+      </c>
+      <c r="J2262">
+        <f>SUM($F$3:F2262)/I2262</f>
+        <v>1.1755637920353963</v>
+      </c>
+      <c r="K2262">
+        <f t="shared" si="95"/>
+        <v>1.8719686800000004</v>
+      </c>
+    </row>
+    <row r="2263" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2263" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B2263">
+        <v>1759.77</v>
+      </c>
+      <c r="C2263">
+        <v>1768.97</v>
+      </c>
+      <c r="D2263">
+        <v>1724.95</v>
+      </c>
+      <c r="E2263">
+        <v>1730.08</v>
+      </c>
+      <c r="F2263">
+        <f t="shared" si="94"/>
+        <v>1.7300799999999998</v>
+      </c>
+      <c r="G2263">
+        <v>273014942</v>
+      </c>
+      <c r="H2263" s="3">
+        <v>574031000000</v>
+      </c>
+      <c r="I2263">
+        <f t="shared" si="91"/>
+        <v>2261</v>
+      </c>
+      <c r="J2263">
+        <f>SUM($F$3:F2263)/I2263</f>
+        <v>1.1758090446704978</v>
+      </c>
+      <c r="K2263">
+        <f t="shared" si="95"/>
+        <v>1.8725227200000005</v>
+      </c>
+    </row>
+    <row r="2264" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2264" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B2264">
+        <v>1724.84</v>
+      </c>
+      <c r="C2264">
+        <v>1730.87</v>
+      </c>
+      <c r="D2264">
+        <v>1677.67</v>
+      </c>
+      <c r="E2264">
+        <v>1682.95</v>
+      </c>
+      <c r="F2264">
+        <f t="shared" si="94"/>
+        <v>1.6829499999999999</v>
+      </c>
+      <c r="G2264">
+        <v>251977336</v>
+      </c>
+      <c r="H2264" s="3">
+        <v>507487000000</v>
+      </c>
+      <c r="I2264">
+        <f t="shared" si="91"/>
+        <v>2262</v>
+      </c>
+      <c r="J2264">
+        <f>SUM($F$3:F2264)/I2264</f>
+        <v>1.1760332449160014</v>
+      </c>
+      <c r="K2264">
+        <f t="shared" si="95"/>
+        <v>1.8727861200000004</v>
+      </c>
+    </row>
+    <row r="2265" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2265" s="1">
+        <v>46211</v>
+      </c>
+      <c r="B2265">
+        <v>1685.12</v>
+      </c>
+      <c r="C2265">
+        <v>1692.09</v>
+      </c>
+      <c r="D2265">
+        <v>1664.94</v>
+      </c>
+      <c r="E2265">
+        <v>1676.99</v>
+      </c>
+      <c r="F2265">
+        <f t="shared" si="94"/>
+        <v>1.67699</v>
+      </c>
+      <c r="G2265">
+        <v>255842616</v>
+      </c>
+      <c r="H2265" s="3">
+        <v>537145000000</v>
+      </c>
+      <c r="I2265">
+        <f t="shared" si="91"/>
+        <v>2263</v>
+      </c>
+      <c r="J2265">
+        <f>SUM($F$3:F2265)/I2265</f>
+        <v>1.1762546133451151</v>
+      </c>
+      <c r="K2265">
+        <f t="shared" si="95"/>
+        <v>1.8730231200000003</v>
+      </c>
+    </row>
+    <row r="2266" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2266" s="1">
+        <v>46212</v>
+      </c>
+      <c r="B2266">
+        <v>1672.18</v>
+      </c>
+      <c r="C2266">
+        <v>1693.59</v>
+      </c>
+      <c r="D2266">
+        <v>1644.53</v>
+      </c>
+      <c r="E2266">
+        <v>1691.75</v>
+      </c>
+      <c r="F2266">
+        <f t="shared" si="94"/>
+        <v>1.6917500000000001</v>
+      </c>
+      <c r="G2266">
+        <v>293992455</v>
+      </c>
+      <c r="H2266" s="3">
+        <v>639759000000</v>
+      </c>
+      <c r="I2266">
+        <f t="shared" si="91"/>
+        <v>2264</v>
+      </c>
+      <c r="J2266">
+        <f>SUM($F$3:F2266)/I2266</f>
+        <v>1.1764823056537081</v>
+      </c>
+      <c r="K2266">
+        <f t="shared" si="95"/>
+        <v>1.8732939200000003</v>
+      </c>
+    </row>
+    <row r="2267" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2267" s="1">
+        <v>46213</v>
+      </c>
+      <c r="B2267">
+        <v>1686.98</v>
+      </c>
+      <c r="C2267">
+        <v>1749.79</v>
+      </c>
+      <c r="D2267">
+        <v>1678.11</v>
+      </c>
+      <c r="E2267">
+        <v>1716.19</v>
+      </c>
+      <c r="F2267">
+        <f t="shared" si="94"/>
+        <v>1.7161900000000001</v>
+      </c>
+      <c r="G2267">
+        <v>359234087</v>
+      </c>
+      <c r="H2267" s="3">
+        <v>766481000000</v>
+      </c>
+      <c r="I2267">
+        <f t="shared" si="91"/>
+        <v>2265</v>
+      </c>
+      <c r="J2267">
+        <f>SUM($F$3:F2267)/I2267</f>
+        <v>1.1767205871964659</v>
+      </c>
+      <c r="K2267">
+        <f t="shared" si="95"/>
+        <v>1.8735534800000007</v>
+      </c>
+    </row>
+    <row r="2268" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2268" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B2268">
+        <v>1706.58</v>
+      </c>
+      <c r="C2268">
+        <v>1712.26</v>
+      </c>
+      <c r="D2268">
+        <v>1634.98</v>
+      </c>
+      <c r="E2268">
+        <v>1639.77</v>
+      </c>
+      <c r="F2268">
+        <f t="shared" si="94"/>
+        <v>1.6397699999999999</v>
+      </c>
+      <c r="G2268">
+        <v>307783620</v>
+      </c>
+      <c r="H2268" s="3">
+        <v>613955000000</v>
+      </c>
+      <c r="I2268">
+        <f t="shared" si="91"/>
+        <v>2266</v>
+      </c>
+      <c r="J2268">
+        <f>SUM($F$3:F2268)/I2268</f>
+        <v>1.1769249338040579</v>
+      </c>
+      <c r="K2268">
+        <f t="shared" si="95"/>
+        <v>1.8735266400000004</v>
+      </c>
+    </row>
+    <row r="2269" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2269" s="1">
+        <v>46217</v>
+      </c>
+      <c r="B2269">
+        <v>1639.66</v>
+      </c>
+      <c r="C2269">
+        <v>1651.1</v>
+      </c>
+      <c r="D2269">
+        <v>1604.61</v>
+      </c>
+      <c r="E2269">
+        <v>1651.1</v>
+      </c>
+      <c r="F2269">
+        <f t="shared" si="94"/>
+        <v>1.6511</v>
+      </c>
+      <c r="G2269">
+        <v>276143649</v>
+      </c>
+      <c r="H2269" s="3">
+        <v>557752000000</v>
+      </c>
+      <c r="I2269">
+        <f t="shared" si="91"/>
+        <v>2267</v>
+      </c>
+      <c r="J2269">
+        <f>SUM($F$3:F2269)/I2269</f>
+        <v>1.1771340979267735</v>
+      </c>
+      <c r="K2269">
+        <f t="shared" si="95"/>
+        <v>1.8736173200000004</v>
+      </c>
+    </row>
+    <row r="2270" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2270" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B2270">
+        <v>1648.49</v>
+      </c>
+      <c r="C2270">
+        <v>1679.32</v>
+      </c>
+      <c r="D2270">
+        <v>1647.31</v>
+      </c>
+      <c r="E2270">
+        <v>1660.39</v>
+      </c>
+      <c r="F2270">
+        <f t="shared" si="94"/>
+        <v>1.66039</v>
+      </c>
+      <c r="G2270">
+        <v>273631213</v>
+      </c>
+      <c r="H2270" s="3">
+        <v>508862000000</v>
+      </c>
+      <c r="I2270">
+        <f t="shared" si="91"/>
+        <v>2268</v>
+      </c>
+      <c r="J2270">
+        <f>SUM($F$3:F2270)/I2270</f>
+        <v>1.1773471737213383</v>
+      </c>
+      <c r="K2270">
+        <f t="shared" si="95"/>
+        <v>1.8737117600000006</v>
+      </c>
+    </row>
+    <row r="2271" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2271" s="1">
+        <v>46219</v>
+      </c>
+      <c r="B2271">
+        <v>1646.91</v>
+      </c>
+      <c r="C2271">
+        <v>1686.28</v>
+      </c>
+      <c r="D2271">
+        <v>1641.8</v>
+      </c>
+      <c r="E2271">
+        <v>1662.43</v>
+      </c>
+      <c r="F2271">
+        <f t="shared" si="94"/>
+        <v>1.6624300000000001</v>
+      </c>
+      <c r="G2271">
+        <v>280118730</v>
+      </c>
+      <c r="H2271" s="3">
+        <v>532148000000</v>
+      </c>
+      <c r="I2271">
+        <f t="shared" si="91"/>
+        <v>2269</v>
+      </c>
+      <c r="J2271">
+        <f>SUM($F$3:F2271)/I2271</f>
+        <v>1.1775609607756701</v>
+      </c>
+      <c r="K2271">
+        <f t="shared" si="95"/>
+        <v>1.8738507200000003</v>
+      </c>
+    </row>
+    <row r="2272" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2272" s="1">
+        <v>46220</v>
+      </c>
+      <c r="B2272">
+        <v>1657.19</v>
+      </c>
+      <c r="C2272">
+        <v>1666.94</v>
+      </c>
+      <c r="D2272">
+        <v>1573.14</v>
+      </c>
+      <c r="E2272">
+        <v>1581.7</v>
+      </c>
+      <c r="F2272">
+        <f t="shared" si="94"/>
+        <v>1.5817000000000001</v>
+      </c>
+      <c r="G2272">
+        <v>313987933</v>
+      </c>
+      <c r="H2272" s="3">
+        <v>572781000000</v>
+      </c>
+      <c r="I2272">
+        <f t="shared" si="91"/>
+        <v>2270</v>
+      </c>
+      <c r="J2272">
+        <f>SUM($F$3:F2272)/I2272</f>
+        <v>1.1777389955947117</v>
+      </c>
+      <c r="K2272">
+        <f t="shared" si="95"/>
+        <v>1.8736343600000007</v>
+      </c>
+    </row>
+    <row r="2273" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2273" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B2273">
+        <v>1592.1</v>
+      </c>
+      <c r="C2273">
+        <v>1614.15</v>
+      </c>
+      <c r="D2273">
+        <v>1525.93</v>
+      </c>
+      <c r="E2273">
+        <v>1553.81</v>
+      </c>
+      <c r="F2273">
+        <f t="shared" si="94"/>
+        <v>1.5538099999999999</v>
+      </c>
+      <c r="G2273">
+        <v>308661368</v>
+      </c>
+      <c r="H2273" s="3">
+        <v>561838000000</v>
+      </c>
+      <c r="I2273">
+        <f t="shared" si="91"/>
+        <v>2271</v>
+      </c>
+      <c r="J2273">
+        <f>SUM($F$3:F2273)/I2273</f>
+        <v>1.1779045926904428</v>
+      </c>
+      <c r="K2273">
+        <f t="shared" si="95"/>
+        <v>1.8732258800000006</v>
+      </c>
+    </row>
+    <row r="2274" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2274" s="1">
+        <v>46224</v>
+      </c>
+      <c r="B2274">
+        <v>1551.23</v>
+      </c>
+      <c r="C2274">
+        <v>1579.76</v>
+      </c>
+      <c r="D2274">
+        <v>1486.84</v>
+      </c>
+      <c r="E2274">
+        <v>1579.76</v>
+      </c>
+      <c r="F2274">
+        <f t="shared" si="94"/>
+        <v>1.5797600000000001</v>
+      </c>
+      <c r="G2274">
+        <v>335361897</v>
+      </c>
+      <c r="H2274" s="3">
+        <v>628475000000</v>
+      </c>
+      <c r="I2274">
+        <f t="shared" si="91"/>
+        <v>2272</v>
+      </c>
+      <c r="J2274">
+        <f>SUM($F$3:F2274)/I2274</f>
+        <v>1.1780814656690122</v>
+      </c>
+      <c r="K2274">
+        <f t="shared" si="95"/>
+        <v>1.8729174800000006</v>
+      </c>
+    </row>
+    <row r="2275" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2275" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B2275">
+        <v>1565.9</v>
+      </c>
+      <c r="C2275">
+        <v>1583.91</v>
+      </c>
+      <c r="D2275">
+        <v>1553.14</v>
+      </c>
+      <c r="E2275">
+        <v>1560.55</v>
+      </c>
+      <c r="F2275">
+        <f t="shared" si="94"/>
+        <v>1.5605499999999999</v>
+      </c>
+      <c r="G2275">
+        <v>279374790</v>
+      </c>
+      <c r="H2275" s="3">
+        <v>582552000000</v>
+      </c>
+      <c r="I2275">
+        <f t="shared" si="91"/>
+        <v>2273</v>
+      </c>
+      <c r="J2275">
+        <f>SUM($F$3:F2275)/I2275</f>
+        <v>1.1782497316322023</v>
+      </c>
+      <c r="K2275">
+        <f t="shared" si="95"/>
+        <v>1.8725264400000003</v>
+      </c>
+    </row>
+    <row r="2276" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2276" s="1">
+        <v>46226</v>
+      </c>
+      <c r="B2276">
+        <v>1556.14</v>
+      </c>
+      <c r="C2276">
+        <v>1579.84</v>
+      </c>
+      <c r="D2276">
+        <v>1550.44</v>
+      </c>
+      <c r="E2276">
+        <v>1579.67</v>
+      </c>
+      <c r="F2276">
+        <f t="shared" si="94"/>
+        <v>1.5796700000000001</v>
+      </c>
+      <c r="G2276">
+        <v>250899709</v>
+      </c>
+      <c r="H2276" s="3">
+        <v>468556000000</v>
+      </c>
+      <c r="I2276">
+        <f t="shared" si="91"/>
+        <v>2274</v>
+      </c>
+      <c r="J2276">
+        <f>SUM($F$3:F2276)/I2276</f>
+        <v>1.1784262576956885</v>
+      </c>
+      <c r="K2276">
+        <f t="shared" si="95"/>
+        <v>1.8721630400000004</v>
+      </c>
+    </row>
+    <row r="2277" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2277" s="1">
+        <v>46227</v>
+      </c>
+      <c r="B2277">
+        <v>1562.86</v>
+      </c>
+      <c r="C2277">
+        <v>1568.54</v>
+      </c>
+      <c r="D2277">
+        <v>1534.18</v>
+      </c>
+      <c r="E2277">
+        <v>1534.2</v>
+      </c>
+      <c r="F2277">
+        <f t="shared" si="94"/>
+        <v>1.5342</v>
+      </c>
+      <c r="G2277">
+        <v>229349469</v>
+      </c>
+      <c r="H2277" s="3">
+        <v>409681000000</v>
+      </c>
+      <c r="I2277">
+        <f t="shared" si="91"/>
+        <v>2275</v>
+      </c>
+      <c r="J2277">
+        <f>SUM($F$3:F2277)/I2277</f>
+        <v>1.1785826417582399</v>
+      </c>
+      <c r="K2277">
+        <f t="shared" si="95"/>
+        <v>1.8716158800000005</v>
+      </c>
+    </row>
+    <row r="2278" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2278" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B2278">
+        <v>1529.52</v>
+      </c>
+      <c r="C2278">
+        <v>1584.5</v>
+      </c>
+      <c r="D2278">
+        <v>1526.92</v>
+      </c>
+      <c r="E2278">
+        <v>1584.5</v>
+      </c>
+      <c r="F2278">
+        <f t="shared" si="94"/>
+        <v>1.5845</v>
+      </c>
+      <c r="G2278">
+        <v>226269293</v>
+      </c>
+      <c r="H2278" s="3">
+        <v>393445000000</v>
+      </c>
+      <c r="I2278">
+        <f t="shared" si="91"/>
+        <v>2276</v>
+      </c>
+      <c r="J2278">
+        <f>SUM($F$3:F2278)/I2278</f>
+        <v>1.1787609885764481</v>
+      </c>
+      <c r="K2278">
+        <f t="shared" si="95"/>
+        <v>1.8712694400000001</v>
+      </c>
+    </row>
+    <row r="2279" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2279" s="1">
+        <v>46231</v>
+      </c>
+      <c r="B2279">
+        <v>1569.71</v>
+      </c>
+      <c r="C2279">
+        <v>1603.21</v>
+      </c>
+      <c r="D2279">
+        <v>1569.16</v>
+      </c>
+      <c r="E2279">
+        <v>1580.54</v>
+      </c>
+      <c r="F2279">
+        <f t="shared" si="94"/>
+        <v>1.5805400000000001</v>
+      </c>
+      <c r="G2279">
+        <v>233577391</v>
+      </c>
+      <c r="H2279" s="3">
+        <v>402509000000</v>
+      </c>
+      <c r="I2279">
+        <f t="shared" si="91"/>
+        <v>2277</v>
+      </c>
+      <c r="J2279">
+        <f>SUM($F$3:F2279)/I2279</f>
+        <v>1.1789374396135246</v>
+      </c>
+      <c r="K2279">
+        <f t="shared" si="95"/>
+        <v>1.8708611600000002</v>
+      </c>
+    </row>
+    <row r="2280" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2280" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B2280">
+        <v>1582.6</v>
+      </c>
+      <c r="C2280">
+        <v>1606.04</v>
+      </c>
+      <c r="D2280">
+        <v>1570.44</v>
+      </c>
+      <c r="E2280">
+        <v>1599.59</v>
+      </c>
+      <c r="F2280">
+        <f t="shared" si="94"/>
+        <v>1.5995899999999998</v>
+      </c>
+      <c r="G2280">
+        <v>272548426</v>
+      </c>
+      <c r="H2280" s="3">
+        <v>460738000000</v>
+      </c>
+      <c r="I2280">
+        <f t="shared" si="91"/>
+        <v>2278</v>
+      </c>
+      <c r="J2280">
+        <f>SUM($F$3:F2280)/I2280</f>
+        <v>1.179122098331868</v>
+      </c>
+      <c r="K2280">
+        <f t="shared" si="95"/>
+        <v>1.8704590800000001</v>
+      </c>
+    </row>
+    <row r="2281" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2281" s="1">
+        <v>46233</v>
+      </c>
+      <c r="B2281">
+        <v>1591.83</v>
+      </c>
+      <c r="C2281">
+        <v>1616.46</v>
+      </c>
+      <c r="D2281">
+        <v>1565.56</v>
+      </c>
+      <c r="E2281">
+        <v>1573.05</v>
+      </c>
+      <c r="F2281">
+        <f t="shared" si="94"/>
+        <v>1.5730500000000001</v>
+      </c>
+      <c r="G2281">
+        <v>288373804</v>
+      </c>
+      <c r="H2281" s="3">
+        <v>465441000000</v>
+      </c>
+      <c r="I2281">
+        <f t="shared" si="91"/>
+        <v>2279</v>
+      </c>
+      <c r="J2281">
+        <f>SUM($F$3:F2281)/I2281</f>
+        <v>1.1792949495392697</v>
+      </c>
+      <c r="K2281">
+        <f t="shared" si="95"/>
+        <v>1.8699379200000001</v>
+      </c>
+    </row>
+    <row r="2282" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2282" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B2282">
+        <v>1593.71</v>
+      </c>
+      <c r="C2282">
+        <v>1653.65</v>
+      </c>
+      <c r="D2282">
+        <v>1593.71</v>
+      </c>
+      <c r="E2282">
+        <v>1638.02</v>
+      </c>
+      <c r="F2282">
+        <f t="shared" si="94"/>
+        <v>1.63802</v>
+      </c>
+      <c r="G2282">
+        <v>331179764</v>
+      </c>
+      <c r="H2282" s="3">
+        <v>574518000000</v>
+      </c>
+      <c r="I2282">
+        <f t="shared" si="91"/>
+        <v>2280</v>
+      </c>
+      <c r="J2282">
+        <f>SUM($F$3:F2282)/I2282</f>
+        <v>1.1794961447368402</v>
+      </c>
+      <c r="K2282">
+        <f t="shared" si="95"/>
+        <v>1.8696278799999997</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/AIinduindex.xlsx
+++ b/lai/valuationquan/AIinduindex.xlsx
@@ -413,7 +413,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K2282"/>
+  <dimension ref="A1:K2303"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
@@ -82475,7 +82475,7 @@
         <v>361445000000</v>
       </c>
       <c r="I2131">
-        <f t="shared" ref="I2131:I2282" si="91">I2130+1</f>
+        <f t="shared" ref="I2131:I2303" si="91">I2130+1</f>
         <v>2129</v>
       </c>
       <c r="J2131">
@@ -84259,7 +84259,7 @@
         <v>2087.19</v>
       </c>
       <c r="F2177">
-        <f t="shared" ref="F2177:F2282" si="94">E2177/1000</f>
+        <f t="shared" ref="F2177:F2303" si="94">E2177/1000</f>
         <v>2.0871900000000001</v>
       </c>
       <c r="G2177">
@@ -86383,7 +86383,7 @@
         <v>1.1668063974876615</v>
       </c>
       <c r="K2231">
-        <f t="shared" ref="K2231:K2282" si="95">SUM(F1982:F2231)/250</f>
+        <f t="shared" ref="K2231:K2303" si="95">SUM(F1982:F2231)/250</f>
         <v>1.8407580399999994</v>
       </c>
     </row>
@@ -88374,6 +88374,825 @@
       <c r="K2282">
         <f t="shared" si="95"/>
         <v>1.8696278799999997</v>
+      </c>
+    </row>
+    <row r="2283" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2283" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B2283">
+        <v>1639.01</v>
+      </c>
+      <c r="C2283">
+        <v>1659.32</v>
+      </c>
+      <c r="D2283">
+        <v>1639.01</v>
+      </c>
+      <c r="E2283">
+        <v>1657.2</v>
+      </c>
+      <c r="F2283">
+        <f t="shared" si="94"/>
+        <v>1.6572</v>
+      </c>
+      <c r="G2283">
+        <v>276427180</v>
+      </c>
+      <c r="H2283" s="3">
+        <v>458359000000</v>
+      </c>
+      <c r="I2283">
+        <f t="shared" si="91"/>
+        <v>2281</v>
+      </c>
+      <c r="J2283">
+        <f>SUM($F$3:F2283)/I2283</f>
+        <v>1.1797055721174903</v>
+      </c>
+      <c r="K2283">
+        <f t="shared" si="95"/>
+        <v>1.8694165999999999</v>
+      </c>
+    </row>
+    <row r="2284" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2284" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B2284">
+        <v>1668.43</v>
+      </c>
+      <c r="C2284">
+        <v>1702.86</v>
+      </c>
+      <c r="D2284">
+        <v>1665.31</v>
+      </c>
+      <c r="E2284">
+        <v>1699.22</v>
+      </c>
+      <c r="F2284">
+        <f t="shared" si="94"/>
+        <v>1.69922</v>
+      </c>
+      <c r="G2284">
+        <v>303489912</v>
+      </c>
+      <c r="H2284" s="3">
+        <v>504185000000</v>
+      </c>
+      <c r="I2284">
+        <f t="shared" si="91"/>
+        <v>2282</v>
+      </c>
+      <c r="J2284">
+        <f>SUM($F$3:F2284)/I2284</f>
+        <v>1.1799332296231355</v>
+      </c>
+      <c r="K2284">
+        <f t="shared" si="95"/>
+        <v>1.8694085599999999</v>
+      </c>
+    </row>
+    <row r="2285" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2285" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B2285">
+        <v>1696.89</v>
+      </c>
+      <c r="C2285">
+        <v>1736.02</v>
+      </c>
+      <c r="D2285">
+        <v>1696.82</v>
+      </c>
+      <c r="E2285">
+        <v>1729.51</v>
+      </c>
+      <c r="F2285">
+        <f t="shared" si="94"/>
+        <v>1.7295099999999999</v>
+      </c>
+      <c r="G2285">
+        <v>345945770</v>
+      </c>
+      <c r="H2285" s="3">
+        <v>604677000000</v>
+      </c>
+      <c r="I2285">
+        <f t="shared" si="91"/>
+        <v>2283</v>
+      </c>
+      <c r="J2285">
+        <f>SUM($F$3:F2285)/I2285</f>
+        <v>1.1801739553219428</v>
+      </c>
+      <c r="K2285">
+        <f t="shared" si="95"/>
+        <v>1.8694421599999995</v>
+      </c>
+    </row>
+    <row r="2286" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2286" s="1">
+        <v>46240</v>
+      </c>
+      <c r="B2286">
+        <v>1718.09</v>
+      </c>
+      <c r="C2286">
+        <v>1742.58</v>
+      </c>
+      <c r="D2286">
+        <v>1710.23</v>
+      </c>
+      <c r="E2286">
+        <v>1733.23</v>
+      </c>
+      <c r="F2286">
+        <f t="shared" si="94"/>
+        <v>1.73323</v>
+      </c>
+      <c r="G2286">
+        <v>314360232</v>
+      </c>
+      <c r="H2286" s="3">
+        <v>538144000000</v>
+      </c>
+      <c r="I2286">
+        <f t="shared" si="91"/>
+        <v>2284</v>
+      </c>
+      <c r="J2286">
+        <f>SUM($F$3:F2286)/I2286</f>
+        <v>1.1804160989492098</v>
+      </c>
+      <c r="K2286">
+        <f t="shared" si="95"/>
+        <v>1.8694261999999997</v>
+      </c>
+    </row>
+    <row r="2287" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2287" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B2287">
+        <v>1731.02</v>
+      </c>
+      <c r="C2287">
+        <v>1740.03</v>
+      </c>
+      <c r="D2287">
+        <v>1697</v>
+      </c>
+      <c r="E2287">
+        <v>1739.96</v>
+      </c>
+      <c r="F2287">
+        <f t="shared" si="94"/>
+        <v>1.73996</v>
+      </c>
+      <c r="G2287">
+        <v>316528362</v>
+      </c>
+      <c r="H2287" s="3">
+        <v>549698000000</v>
+      </c>
+      <c r="I2287">
+        <f t="shared" si="91"/>
+        <v>2285</v>
+      </c>
+      <c r="J2287">
+        <f>SUM($F$3:F2287)/I2287</f>
+        <v>1.180660975929976</v>
+      </c>
+      <c r="K2287">
+        <f t="shared" si="95"/>
+        <v>1.8694150799999996</v>
+      </c>
+    </row>
+    <row r="2288" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2288" s="1">
+        <v>46244</v>
+      </c>
+      <c r="B2288">
+        <v>1742.85</v>
+      </c>
+      <c r="C2288">
+        <v>1756.74</v>
+      </c>
+      <c r="D2288">
+        <v>1725.27</v>
+      </c>
+      <c r="E2288">
+        <v>1756.74</v>
+      </c>
+      <c r="F2288">
+        <f t="shared" si="94"/>
+        <v>1.75674</v>
+      </c>
+      <c r="G2288">
+        <v>271501367</v>
+      </c>
+      <c r="H2288" s="3">
+        <v>477178000000</v>
+      </c>
+      <c r="I2288">
+        <f t="shared" si="91"/>
+        <v>2286</v>
+      </c>
+      <c r="J2288">
+        <f>SUM($F$3:F2288)/I2288</f>
+        <v>1.1809129790026225</v>
+      </c>
+      <c r="K2288">
+        <f t="shared" si="95"/>
+        <v>1.8694515999999994</v>
+      </c>
+    </row>
+    <row r="2289" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2289" s="1">
+        <v>46245</v>
+      </c>
+      <c r="B2289">
+        <v>1751.5</v>
+      </c>
+      <c r="C2289">
+        <v>1765.09</v>
+      </c>
+      <c r="D2289">
+        <v>1733.94</v>
+      </c>
+      <c r="E2289">
+        <v>1750.11</v>
+      </c>
+      <c r="F2289">
+        <f t="shared" si="94"/>
+        <v>1.7501099999999998</v>
+      </c>
+      <c r="G2289">
+        <v>250756722</v>
+      </c>
+      <c r="H2289" s="3">
+        <v>436729000000</v>
+      </c>
+      <c r="I2289">
+        <f t="shared" si="91"/>
+        <v>2287</v>
+      </c>
+      <c r="J2289">
+        <f>SUM($F$3:F2289)/I2289</f>
+        <v>1.1811618627022278</v>
+      </c>
+      <c r="K2289">
+        <f t="shared" si="95"/>
+        <v>1.8695190799999994</v>
+      </c>
+    </row>
+    <row r="2290" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2290" s="1">
+        <v>46246</v>
+      </c>
+      <c r="B2290">
+        <v>1751.58</v>
+      </c>
+      <c r="C2290">
+        <v>1770.91</v>
+      </c>
+      <c r="D2290">
+        <v>1748.17</v>
+      </c>
+      <c r="E2290">
+        <v>1770.33</v>
+      </c>
+      <c r="F2290">
+        <f t="shared" si="94"/>
+        <v>1.77033</v>
+      </c>
+      <c r="G2290">
+        <v>254604452</v>
+      </c>
+      <c r="H2290" s="3">
+        <v>424426000000</v>
+      </c>
+      <c r="I2290">
+        <f t="shared" si="91"/>
+        <v>2288</v>
+      </c>
+      <c r="J2290">
+        <f>SUM($F$3:F2290)/I2290</f>
+        <v>1.1814193662587391</v>
+      </c>
+      <c r="K2290">
+        <f t="shared" si="95"/>
+        <v>1.8696845999999996</v>
+      </c>
+    </row>
+    <row r="2291" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2291" s="1">
+        <v>46247</v>
+      </c>
+      <c r="B2291">
+        <v>1776.7</v>
+      </c>
+      <c r="C2291">
+        <v>1789.06</v>
+      </c>
+      <c r="D2291">
+        <v>1752.98</v>
+      </c>
+      <c r="E2291">
+        <v>1752.98</v>
+      </c>
+      <c r="F2291">
+        <f t="shared" si="94"/>
+        <v>1.75298</v>
+      </c>
+      <c r="G2291">
+        <v>318340035</v>
+      </c>
+      <c r="H2291" s="3">
+        <v>555547000000</v>
+      </c>
+      <c r="I2291">
+        <f t="shared" si="91"/>
+        <v>2289</v>
+      </c>
+      <c r="J2291">
+        <f>SUM($F$3:F2291)/I2291</f>
+        <v>1.1816690650939252</v>
+      </c>
+      <c r="K2291">
+        <f t="shared" si="95"/>
+        <v>1.8697199599999994</v>
+      </c>
+    </row>
+    <row r="2292" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2292" s="1">
+        <v>46248</v>
+      </c>
+      <c r="B2292">
+        <v>1754.82</v>
+      </c>
+      <c r="C2292">
+        <v>1761.33</v>
+      </c>
+      <c r="D2292">
+        <v>1732.37</v>
+      </c>
+      <c r="E2292">
+        <v>1754.7</v>
+      </c>
+      <c r="F2292">
+        <f t="shared" si="94"/>
+        <v>1.7547000000000001</v>
+      </c>
+      <c r="G2292">
+        <v>279400691</v>
+      </c>
+      <c r="H2292" s="3">
+        <v>468149000000</v>
+      </c>
+      <c r="I2292">
+        <f t="shared" si="91"/>
+        <v>2290</v>
+      </c>
+      <c r="J2292">
+        <f>SUM($F$3:F2292)/I2292</f>
+        <v>1.1819192969432293</v>
+      </c>
+      <c r="K2292">
+        <f t="shared" si="95"/>
+        <v>1.8696744799999994</v>
+      </c>
+    </row>
+    <row r="2293" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2293" s="1">
+        <v>46251</v>
+      </c>
+      <c r="B2293">
+        <v>1755.55</v>
+      </c>
+      <c r="C2293">
+        <v>1777.58</v>
+      </c>
+      <c r="D2293">
+        <v>1737.26</v>
+      </c>
+      <c r="E2293">
+        <v>1777.58</v>
+      </c>
+      <c r="F2293">
+        <f t="shared" si="94"/>
+        <v>1.7775799999999999</v>
+      </c>
+      <c r="G2293">
+        <v>258025091</v>
+      </c>
+      <c r="H2293" s="3">
+        <v>484596000000</v>
+      </c>
+      <c r="I2293">
+        <f t="shared" si="91"/>
+        <v>2291</v>
+      </c>
+      <c r="J2293">
+        <f>SUM($F$3:F2293)/I2293</f>
+        <v>1.1821792972501068</v>
+      </c>
+      <c r="K2293">
+        <f t="shared" si="95"/>
+        <v>1.8696787999999993</v>
+      </c>
+    </row>
+    <row r="2294" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2294" s="1">
+        <v>46252</v>
+      </c>
+      <c r="B2294">
+        <v>1774.98</v>
+      </c>
+      <c r="C2294">
+        <v>1774.98</v>
+      </c>
+      <c r="D2294">
+        <v>1746.13</v>
+      </c>
+      <c r="E2294">
+        <v>1766.39</v>
+      </c>
+      <c r="F2294">
+        <f t="shared" si="94"/>
+        <v>1.7663900000000001</v>
+      </c>
+      <c r="G2294">
+        <v>266492186</v>
+      </c>
+      <c r="H2294" s="3">
+        <v>480354000000</v>
+      </c>
+      <c r="I2294">
+        <f t="shared" si="91"/>
+        <v>2292</v>
+      </c>
+      <c r="J2294">
+        <f>SUM($F$3:F2294)/I2294</f>
+        <v>1.1824341884816731</v>
+      </c>
+      <c r="K2294">
+        <f t="shared" si="95"/>
+        <v>1.8695519999999992</v>
+      </c>
+    </row>
+    <row r="2295" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2295" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B2295">
+        <v>1746.1</v>
+      </c>
+      <c r="C2295">
+        <v>1746.11</v>
+      </c>
+      <c r="D2295">
+        <v>1680.37</v>
+      </c>
+      <c r="E2295">
+        <v>1683.98</v>
+      </c>
+      <c r="F2295">
+        <f t="shared" si="94"/>
+        <v>1.68398</v>
+      </c>
+      <c r="G2295">
+        <v>269982120</v>
+      </c>
+      <c r="H2295" s="3">
+        <v>493521000000</v>
+      </c>
+      <c r="I2295">
+        <f t="shared" si="91"/>
+        <v>2293</v>
+      </c>
+      <c r="J2295">
+        <f>SUM($F$3:F2295)/I2295</f>
+        <v>1.1826529175752265</v>
+      </c>
+      <c r="K2295">
+        <f t="shared" si="95"/>
+        <v>1.8690901999999996</v>
+      </c>
+    </row>
+    <row r="2296" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2296" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B2296">
+        <v>1700.82</v>
+      </c>
+      <c r="C2296">
+        <v>1721.37</v>
+      </c>
+      <c r="D2296">
+        <v>1693.95</v>
+      </c>
+      <c r="E2296">
+        <v>1709.08</v>
+      </c>
+      <c r="F2296">
+        <f t="shared" si="94"/>
+        <v>1.7090799999999999</v>
+      </c>
+      <c r="G2296">
+        <v>218817454</v>
+      </c>
+      <c r="H2296" s="3">
+        <v>385100000000</v>
+      </c>
+      <c r="I2296">
+        <f t="shared" si="91"/>
+        <v>2294</v>
+      </c>
+      <c r="J2296">
+        <f>SUM($F$3:F2296)/I2296</f>
+        <v>1.1828823975588467</v>
+      </c>
+      <c r="K2296">
+        <f t="shared" si="95"/>
+        <v>1.8688062399999994</v>
+      </c>
+    </row>
+    <row r="2297" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2297" s="1">
+        <v>46255</v>
+      </c>
+      <c r="B2297">
+        <v>1698.86</v>
+      </c>
+      <c r="C2297">
+        <v>1710.12</v>
+      </c>
+      <c r="D2297">
+        <v>1677.22</v>
+      </c>
+      <c r="E2297">
+        <v>1706.22</v>
+      </c>
+      <c r="F2297">
+        <f t="shared" si="94"/>
+        <v>1.7062200000000001</v>
+      </c>
+      <c r="G2297">
+        <v>192505480</v>
+      </c>
+      <c r="H2297" s="3">
+        <v>332974000000</v>
+      </c>
+      <c r="I2297">
+        <f t="shared" si="91"/>
+        <v>2295</v>
+      </c>
+      <c r="J2297">
+        <f>SUM($F$3:F2297)/I2297</f>
+        <v>1.1831104313725467</v>
+      </c>
+      <c r="K2297">
+        <f t="shared" si="95"/>
+        <v>1.8684073199999995</v>
+      </c>
+    </row>
+    <row r="2298" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2298" s="1">
+        <v>46258</v>
+      </c>
+      <c r="B2298">
+        <v>1707.02</v>
+      </c>
+      <c r="C2298">
+        <v>1711.18</v>
+      </c>
+      <c r="D2298">
+        <v>1662.5</v>
+      </c>
+      <c r="E2298">
+        <v>1680.12</v>
+      </c>
+      <c r="F2298">
+        <f t="shared" si="94"/>
+        <v>1.6801199999999998</v>
+      </c>
+      <c r="G2298">
+        <v>204277164</v>
+      </c>
+      <c r="H2298" s="3">
+        <v>354225000000</v>
+      </c>
+      <c r="I2298">
+        <f t="shared" si="91"/>
+        <v>2296</v>
+      </c>
+      <c r="J2298">
+        <f>SUM($F$3:F2298)/I2298</f>
+        <v>1.1833268989547014</v>
+      </c>
+      <c r="K2298">
+        <f t="shared" si="95"/>
+        <v>1.8679040799999991</v>
+      </c>
+    </row>
+    <row r="2299" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2299" s="1">
+        <v>46259</v>
+      </c>
+      <c r="B2299">
+        <v>1670.58</v>
+      </c>
+      <c r="C2299">
+        <v>1716.13</v>
+      </c>
+      <c r="D2299">
+        <v>1666.49</v>
+      </c>
+      <c r="E2299">
+        <v>1711.79</v>
+      </c>
+      <c r="F2299">
+        <f t="shared" si="94"/>
+        <v>1.7117899999999999</v>
+      </c>
+      <c r="G2299">
+        <v>195708480</v>
+      </c>
+      <c r="H2299" s="3">
+        <v>319286000000</v>
+      </c>
+      <c r="I2299">
+        <f t="shared" si="91"/>
+        <v>2297</v>
+      </c>
+      <c r="J2299">
+        <f>SUM($F$3:F2299)/I2299</f>
+        <v>1.1835569656073115</v>
+      </c>
+      <c r="K2299">
+        <f t="shared" si="95"/>
+        <v>1.8674799999999991</v>
+      </c>
+    </row>
+    <row r="2300" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2300" s="1">
+        <v>46260</v>
+      </c>
+      <c r="B2300">
+        <v>1710.57</v>
+      </c>
+      <c r="C2300">
+        <v>1719.68</v>
+      </c>
+      <c r="D2300">
+        <v>1695.76</v>
+      </c>
+      <c r="E2300">
+        <v>1710.55</v>
+      </c>
+      <c r="F2300">
+        <f t="shared" si="94"/>
+        <v>1.71055</v>
+      </c>
+      <c r="G2300">
+        <v>192939899</v>
+      </c>
+      <c r="H2300" s="3">
+        <v>317037000000</v>
+      </c>
+      <c r="I2300">
+        <f t="shared" si="91"/>
+        <v>2298</v>
+      </c>
+      <c r="J2300">
+        <f>SUM($F$3:F2300)/I2300</f>
+        <v>1.1837862924281959</v>
+      </c>
+      <c r="K2300">
+        <f t="shared" si="95"/>
+        <v>1.867153319999999</v>
+      </c>
+    </row>
+    <row r="2301" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2301" s="1">
+        <v>46261</v>
+      </c>
+      <c r="B2301">
+        <v>1708.38</v>
+      </c>
+      <c r="C2301">
+        <v>1728.52</v>
+      </c>
+      <c r="D2301">
+        <v>1705.38</v>
+      </c>
+      <c r="E2301">
+        <v>1728.52</v>
+      </c>
+      <c r="F2301">
+        <f t="shared" si="94"/>
+        <v>1.7285200000000001</v>
+      </c>
+      <c r="G2301">
+        <v>218139037</v>
+      </c>
+      <c r="H2301" s="3">
+        <v>387606000000</v>
+      </c>
+      <c r="I2301">
+        <f t="shared" si="91"/>
+        <v>2299</v>
+      </c>
+      <c r="J2301">
+        <f>SUM($F$3:F2301)/I2301</f>
+        <v>1.1840232361896452</v>
+      </c>
+      <c r="K2301">
+        <f t="shared" si="95"/>
+        <v>1.8667706799999992</v>
+      </c>
+    </row>
+    <row r="2302" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2302" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B2302">
+        <v>1731.17</v>
+      </c>
+      <c r="C2302">
+        <v>1748.44</v>
+      </c>
+      <c r="D2302">
+        <v>1729.34</v>
+      </c>
+      <c r="E2302">
+        <v>1729.75</v>
+      </c>
+      <c r="F2302">
+        <f t="shared" si="94"/>
+        <v>1.7297499999999999</v>
+      </c>
+      <c r="G2302">
+        <v>228036691</v>
+      </c>
+      <c r="H2302" s="3">
+        <v>390257000000</v>
+      </c>
+      <c r="I2302">
+        <f t="shared" si="91"/>
+        <v>2300</v>
+      </c>
+      <c r="J2302">
+        <f>SUM($F$3:F2302)/I2302</f>
+        <v>1.1842605086956497</v>
+      </c>
+      <c r="K2302">
+        <f t="shared" si="95"/>
+        <v>1.8662258399999989</v>
+      </c>
+    </row>
+    <row r="2303" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2303" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B2303">
+        <v>1713.66</v>
+      </c>
+      <c r="C2303">
+        <v>1758.69</v>
+      </c>
+      <c r="D2303">
+        <v>1712.78</v>
+      </c>
+      <c r="E2303">
+        <v>1758.22</v>
+      </c>
+      <c r="F2303">
+        <f t="shared" si="94"/>
+        <v>1.7582200000000001</v>
+      </c>
+      <c r="G2303">
+        <v>261631654</v>
+      </c>
+      <c r="H2303" s="3">
+        <v>440341000000</v>
+      </c>
+      <c r="I2303">
+        <f t="shared" si="91"/>
+        <v>2301</v>
+      </c>
+      <c r="J2303">
+        <f>SUM($F$3:F2303)/I2303</f>
+        <v>1.1845099478487591</v>
+      </c>
+      <c r="K2303">
+        <f t="shared" si="95"/>
+        <v>1.8657503599999992</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/AIinduindex.xlsx
+++ b/lai/valuationquan/AIinduindex.xlsx
@@ -413,7 +413,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K2303"/>
+  <dimension ref="A1:K2324"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
@@ -82475,7 +82475,7 @@
         <v>361445000000</v>
       </c>
       <c r="I2131">
-        <f t="shared" ref="I2131:I2303" si="91">I2130+1</f>
+        <f t="shared" ref="I2131:I2324" si="91">I2130+1</f>
         <v>2129</v>
       </c>
       <c r="J2131">
@@ -84259,7 +84259,7 @@
         <v>2087.19</v>
       </c>
       <c r="F2177">
-        <f t="shared" ref="F2177:F2303" si="94">E2177/1000</f>
+        <f t="shared" ref="F2177:F2324" si="94">E2177/1000</f>
         <v>2.0871900000000001</v>
       </c>
       <c r="G2177">
@@ -86383,7 +86383,7 @@
         <v>1.1668063974876615</v>
       </c>
       <c r="K2231">
-        <f t="shared" ref="K2231:K2303" si="95">SUM(F1982:F2231)/250</f>
+        <f t="shared" ref="K2231:K2324" si="95">SUM(F1982:F2231)/250</f>
         <v>1.8407580399999994</v>
       </c>
     </row>
@@ -89193,6 +89193,825 @@
       <c r="K2303">
         <f t="shared" si="95"/>
         <v>1.8657503599999992</v>
+      </c>
+    </row>
+    <row r="2304" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2304" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B2304">
+        <v>1759.16</v>
+      </c>
+      <c r="C2304">
+        <v>1780.48</v>
+      </c>
+      <c r="D2304">
+        <v>1758.4</v>
+      </c>
+      <c r="E2304">
+        <v>1775.92</v>
+      </c>
+      <c r="F2304">
+        <f t="shared" si="94"/>
+        <v>1.7759200000000002</v>
+      </c>
+      <c r="G2304">
+        <v>284831151</v>
+      </c>
+      <c r="H2304" s="3">
+        <v>434633000000</v>
+      </c>
+      <c r="I2304">
+        <f t="shared" si="91"/>
+        <v>2302</v>
+      </c>
+      <c r="J2304">
+        <f>SUM($F$3:F2304)/I2304</f>
+        <v>1.1847668592528213</v>
+      </c>
+      <c r="K2304">
+        <f t="shared" si="95"/>
+        <v>1.8653186799999992</v>
+      </c>
+    </row>
+    <row r="2305" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2305" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B2305">
+        <v>1762.69</v>
+      </c>
+      <c r="C2305">
+        <v>1770.41</v>
+      </c>
+      <c r="D2305">
+        <v>1749.34</v>
+      </c>
+      <c r="E2305">
+        <v>1761.84</v>
+      </c>
+      <c r="F2305">
+        <f t="shared" si="94"/>
+        <v>1.7618399999999999</v>
+      </c>
+      <c r="G2305">
+        <v>235593397</v>
+      </c>
+      <c r="H2305" s="3">
+        <v>363527000000</v>
+      </c>
+      <c r="I2305">
+        <f t="shared" si="91"/>
+        <v>2303</v>
+      </c>
+      <c r="J2305">
+        <f>SUM($F$3:F2305)/I2305</f>
+        <v>1.1850174337820212</v>
+      </c>
+      <c r="K2305">
+        <f t="shared" si="95"/>
+        <v>1.8648453199999993</v>
+      </c>
+    </row>
+    <row r="2306" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2306" s="1">
+        <v>46268</v>
+      </c>
+      <c r="B2306">
+        <v>1769.21</v>
+      </c>
+      <c r="C2306">
+        <v>1777.3</v>
+      </c>
+      <c r="D2306">
+        <v>1743.23</v>
+      </c>
+      <c r="E2306">
+        <v>1750.66</v>
+      </c>
+      <c r="F2306">
+        <f t="shared" si="94"/>
+        <v>1.7506600000000001</v>
+      </c>
+      <c r="G2306">
+        <v>221613255</v>
+      </c>
+      <c r="H2306" s="3">
+        <v>346944000000</v>
+      </c>
+      <c r="I2306">
+        <f t="shared" si="91"/>
+        <v>2304</v>
+      </c>
+      <c r="J2306">
+        <f>SUM($F$3:F2306)/I2306</f>
+        <v>1.1852629383680533</v>
+      </c>
+      <c r="K2306">
+        <f t="shared" si="95"/>
+        <v>1.864217239999999</v>
+      </c>
+    </row>
+    <row r="2307" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2307" s="1">
+        <v>46269</v>
+      </c>
+      <c r="B2307">
+        <v>1762.7</v>
+      </c>
+      <c r="C2307">
+        <v>1790.91</v>
+      </c>
+      <c r="D2307">
+        <v>1744.95</v>
+      </c>
+      <c r="E2307">
+        <v>1754.56</v>
+      </c>
+      <c r="F2307">
+        <f t="shared" si="94"/>
+        <v>1.7545599999999999</v>
+      </c>
+      <c r="G2307">
+        <v>282363682</v>
+      </c>
+      <c r="H2307" s="3">
+        <v>456041000000</v>
+      </c>
+      <c r="I2307">
+        <f t="shared" si="91"/>
+        <v>2305</v>
+      </c>
+      <c r="J2307">
+        <f>SUM($F$3:F2307)/I2307</f>
+        <v>1.1855099219088914</v>
+      </c>
+      <c r="K2307">
+        <f t="shared" si="95"/>
+        <v>1.8635082799999989</v>
+      </c>
+    </row>
+    <row r="2308" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2308" s="1">
+        <v>46272</v>
+      </c>
+      <c r="B2308">
+        <v>1757.48</v>
+      </c>
+      <c r="C2308">
+        <v>1766.03</v>
+      </c>
+      <c r="D2308">
+        <v>1749.11</v>
+      </c>
+      <c r="E2308">
+        <v>1763.75</v>
+      </c>
+      <c r="F2308">
+        <f t="shared" si="94"/>
+        <v>1.7637499999999999</v>
+      </c>
+      <c r="G2308">
+        <v>236727488</v>
+      </c>
+      <c r="H2308" s="3">
+        <v>401526000000</v>
+      </c>
+      <c r="I2308">
+        <f t="shared" si="91"/>
+        <v>2306</v>
+      </c>
+      <c r="J2308">
+        <f>SUM($F$3:F2308)/I2308</f>
+        <v>1.1857606764960948</v>
+      </c>
+      <c r="K2308">
+        <f t="shared" si="95"/>
+        <v>1.8627985599999988</v>
+      </c>
+    </row>
+    <row r="2309" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2309" s="1">
+        <v>46273</v>
+      </c>
+      <c r="B2309">
+        <v>1764.96</v>
+      </c>
+      <c r="C2309">
+        <v>1776.06</v>
+      </c>
+      <c r="D2309">
+        <v>1758.21</v>
+      </c>
+      <c r="E2309">
+        <v>1771.54</v>
+      </c>
+      <c r="F2309">
+        <f t="shared" si="94"/>
+        <v>1.7715399999999999</v>
+      </c>
+      <c r="G2309">
+        <v>240740031</v>
+      </c>
+      <c r="H2309" s="3">
+        <v>389362000000</v>
+      </c>
+      <c r="I2309">
+        <f t="shared" si="91"/>
+        <v>2307</v>
+      </c>
+      <c r="J2309">
+        <f>SUM($F$3:F2309)/I2309</f>
+        <v>1.1860145903771109</v>
+      </c>
+      <c r="K2309">
+        <f t="shared" si="95"/>
+        <v>1.8622713599999992</v>
+      </c>
+    </row>
+    <row r="2310" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2310" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B2310">
+        <v>1767.55</v>
+      </c>
+      <c r="C2310">
+        <v>1767.7</v>
+      </c>
+      <c r="D2310">
+        <v>1742.01</v>
+      </c>
+      <c r="E2310">
+        <v>1751</v>
+      </c>
+      <c r="F2310">
+        <f t="shared" si="94"/>
+        <v>1.7509999999999999</v>
+      </c>
+      <c r="G2310">
+        <v>218686707</v>
+      </c>
+      <c r="H2310" s="3">
+        <v>333728000000</v>
+      </c>
+      <c r="I2310">
+        <f t="shared" si="91"/>
+        <v>2308</v>
+      </c>
+      <c r="J2310">
+        <f>SUM($F$3:F2310)/I2310</f>
+        <v>1.186259384748698</v>
+      </c>
+      <c r="K2310">
+        <f t="shared" si="95"/>
+        <v>1.8615984799999989</v>
+      </c>
+    </row>
+    <row r="2311" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2311" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B2311">
+        <v>1743.56</v>
+      </c>
+      <c r="C2311">
+        <v>1743.61</v>
+      </c>
+      <c r="D2311">
+        <v>1726.6</v>
+      </c>
+      <c r="E2311">
+        <v>1729.19</v>
+      </c>
+      <c r="F2311">
+        <f t="shared" si="94"/>
+        <v>1.72919</v>
+      </c>
+      <c r="G2311">
+        <v>187662092</v>
+      </c>
+      <c r="H2311" s="3">
+        <v>286721000000</v>
+      </c>
+      <c r="I2311">
+        <f t="shared" si="91"/>
+        <v>2309</v>
+      </c>
+      <c r="J2311">
+        <f>SUM($F$3:F2311)/I2311</f>
+        <v>1.1864945214378497</v>
+      </c>
+      <c r="K2311">
+        <f t="shared" si="95"/>
+        <v>1.8609088799999989</v>
+      </c>
+    </row>
+    <row r="2312" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2312" s="1">
+        <v>46276</v>
+      </c>
+      <c r="B2312">
+        <v>1716.76</v>
+      </c>
+      <c r="C2312">
+        <v>1716.76</v>
+      </c>
+      <c r="D2312">
+        <v>1675.32</v>
+      </c>
+      <c r="E2312">
+        <v>1697.23</v>
+      </c>
+      <c r="F2312">
+        <f t="shared" si="94"/>
+        <v>1.69723</v>
+      </c>
+      <c r="G2312">
+        <v>228177886</v>
+      </c>
+      <c r="H2312" s="3">
+        <v>342811000000</v>
+      </c>
+      <c r="I2312">
+        <f t="shared" si="91"/>
+        <v>2310</v>
+      </c>
+      <c r="J2312">
+        <f>SUM($F$3:F2312)/I2312</f>
+        <v>1.1867156190476171</v>
+      </c>
+      <c r="K2312">
+        <f t="shared" si="95"/>
+        <v>1.8600331599999993</v>
+      </c>
+    </row>
+    <row r="2313" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2313" s="1">
+        <v>46279</v>
+      </c>
+      <c r="B2313">
+        <v>1694.73</v>
+      </c>
+      <c r="C2313">
+        <v>1714.37</v>
+      </c>
+      <c r="D2313">
+        <v>1689.1</v>
+      </c>
+      <c r="E2313">
+        <v>1706.67</v>
+      </c>
+      <c r="F2313">
+        <f t="shared" si="94"/>
+        <v>1.7066700000000001</v>
+      </c>
+      <c r="G2313">
+        <v>186608940</v>
+      </c>
+      <c r="H2313" s="3">
+        <v>283432000000</v>
+      </c>
+      <c r="I2313">
+        <f t="shared" si="91"/>
+        <v>2311</v>
+      </c>
+      <c r="J2313">
+        <f>SUM($F$3:F2313)/I2313</f>
+        <v>1.1869406101254849</v>
+      </c>
+      <c r="K2313">
+        <f t="shared" si="95"/>
+        <v>1.859401879999999</v>
+      </c>
+    </row>
+    <row r="2314" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2314" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B2314">
+        <v>1708.65</v>
+      </c>
+      <c r="C2314">
+        <v>1709.35</v>
+      </c>
+      <c r="D2314">
+        <v>1681.29</v>
+      </c>
+      <c r="E2314">
+        <v>1682.13</v>
+      </c>
+      <c r="F2314">
+        <f t="shared" si="94"/>
+        <v>1.6821300000000001</v>
+      </c>
+      <c r="G2314">
+        <v>189019682</v>
+      </c>
+      <c r="H2314" s="3">
+        <v>283797000000</v>
+      </c>
+      <c r="I2314">
+        <f t="shared" si="91"/>
+        <v>2312</v>
+      </c>
+      <c r="J2314">
+        <f>SUM($F$3:F2314)/I2314</f>
+        <v>1.1871547923875414</v>
+      </c>
+      <c r="K2314">
+        <f t="shared" si="95"/>
+        <v>1.8588400399999989</v>
+      </c>
+    </row>
+    <row r="2315" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2315" s="1">
+        <v>46281</v>
+      </c>
+      <c r="B2315">
+        <v>1677.56</v>
+      </c>
+      <c r="C2315">
+        <v>1706.8</v>
+      </c>
+      <c r="D2315">
+        <v>1668.13</v>
+      </c>
+      <c r="E2315">
+        <v>1703.95</v>
+      </c>
+      <c r="F2315">
+        <f t="shared" si="94"/>
+        <v>1.7039500000000001</v>
+      </c>
+      <c r="G2315">
+        <v>191469120</v>
+      </c>
+      <c r="H2315" s="3">
+        <v>320838000000</v>
+      </c>
+      <c r="I2315">
+        <f t="shared" si="91"/>
+        <v>2313</v>
+      </c>
+      <c r="J2315">
+        <f>SUM($F$3:F2315)/I2315</f>
+        <v>1.1873782230868983</v>
+      </c>
+      <c r="K2315">
+        <f t="shared" si="95"/>
+        <v>1.858467479999999</v>
+      </c>
+    </row>
+    <row r="2316" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2316" s="1">
+        <v>46282</v>
+      </c>
+      <c r="B2316">
+        <v>1697.92</v>
+      </c>
+      <c r="C2316">
+        <v>1711.64</v>
+      </c>
+      <c r="D2316">
+        <v>1693.71</v>
+      </c>
+      <c r="E2316">
+        <v>1708.6</v>
+      </c>
+      <c r="F2316">
+        <f t="shared" si="94"/>
+        <v>1.7085999999999999</v>
+      </c>
+      <c r="G2316">
+        <v>203474614</v>
+      </c>
+      <c r="H2316" s="3">
+        <v>329414000000</v>
+      </c>
+      <c r="I2316">
+        <f t="shared" si="91"/>
+        <v>2314</v>
+      </c>
+      <c r="J2316">
+        <f>SUM($F$3:F2316)/I2316</f>
+        <v>1.1876034701815019</v>
+      </c>
+      <c r="K2316">
+        <f t="shared" si="95"/>
+        <v>1.8579466399999989</v>
+      </c>
+    </row>
+    <row r="2317" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2317" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B2317">
+        <v>1718.97</v>
+      </c>
+      <c r="C2317">
+        <v>1739.93</v>
+      </c>
+      <c r="D2317">
+        <v>1718.97</v>
+      </c>
+      <c r="E2317">
+        <v>1737.83</v>
+      </c>
+      <c r="F2317">
+        <f t="shared" si="94"/>
+        <v>1.73783</v>
+      </c>
+      <c r="G2317">
+        <v>225705400</v>
+      </c>
+      <c r="H2317" s="3">
+        <v>399913000000</v>
+      </c>
+      <c r="I2317">
+        <f t="shared" si="91"/>
+        <v>2315</v>
+      </c>
+      <c r="J2317">
+        <f>SUM($F$3:F2317)/I2317</f>
+        <v>1.1878411490280758</v>
+      </c>
+      <c r="K2317">
+        <f t="shared" si="95"/>
+        <v>1.8574539999999988</v>
+      </c>
+    </row>
+    <row r="2318" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2318" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B2318">
+        <v>1745.08</v>
+      </c>
+      <c r="C2318">
+        <v>1770.99</v>
+      </c>
+      <c r="D2318">
+        <v>1744.66</v>
+      </c>
+      <c r="E2318">
+        <v>1770.91</v>
+      </c>
+      <c r="F2318">
+        <f t="shared" si="94"/>
+        <v>1.77091</v>
+      </c>
+      <c r="G2318">
+        <v>239180556</v>
+      </c>
+      <c r="H2318" s="3">
+        <v>395112000000</v>
+      </c>
+      <c r="I2318">
+        <f t="shared" si="91"/>
+        <v>2316</v>
+      </c>
+      <c r="J2318">
+        <f>SUM($F$3:F2318)/I2318</f>
+        <v>1.1880929058721916</v>
+      </c>
+      <c r="K2318">
+        <f t="shared" si="95"/>
+        <v>1.8572117599999991</v>
+      </c>
+    </row>
+    <row r="2319" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2319" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B2319">
+        <v>1780.91</v>
+      </c>
+      <c r="C2319">
+        <v>1800.69</v>
+      </c>
+      <c r="D2319">
+        <v>1779.56</v>
+      </c>
+      <c r="E2319">
+        <v>1788.74</v>
+      </c>
+      <c r="F2319">
+        <f t="shared" si="94"/>
+        <v>1.78874</v>
+      </c>
+      <c r="G2319">
+        <v>264645562</v>
+      </c>
+      <c r="H2319" s="3">
+        <v>470821000000</v>
+      </c>
+      <c r="I2319">
+        <f t="shared" si="91"/>
+        <v>2317</v>
+      </c>
+      <c r="J2319">
+        <f>SUM($F$3:F2319)/I2319</f>
+        <v>1.1883521406991782</v>
+      </c>
+      <c r="K2319">
+        <f t="shared" si="95"/>
+        <v>1.8569903199999995</v>
+      </c>
+    </row>
+    <row r="2320" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2320" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B2320">
+        <v>1786.94</v>
+      </c>
+      <c r="C2320">
+        <v>1786.95</v>
+      </c>
+      <c r="D2320">
+        <v>1771.54</v>
+      </c>
+      <c r="E2320">
+        <v>1774.08</v>
+      </c>
+      <c r="F2320">
+        <f t="shared" si="94"/>
+        <v>1.7740799999999999</v>
+      </c>
+      <c r="G2320">
+        <v>232753706</v>
+      </c>
+      <c r="H2320" s="3">
+        <v>362488000000</v>
+      </c>
+      <c r="I2320">
+        <f t="shared" si="91"/>
+        <v>2318</v>
+      </c>
+      <c r="J2320">
+        <f>SUM($F$3:F2320)/I2320</f>
+        <v>1.1886048274374443</v>
+      </c>
+      <c r="K2320">
+        <f t="shared" si="95"/>
+        <v>1.856561119999999</v>
+      </c>
+    </row>
+    <row r="2321" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2321" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B2321">
+        <v>1768.93</v>
+      </c>
+      <c r="C2321">
+        <v>1776.96</v>
+      </c>
+      <c r="D2321">
+        <v>1752.04</v>
+      </c>
+      <c r="E2321">
+        <v>1753.2</v>
+      </c>
+      <c r="F2321">
+        <f t="shared" si="94"/>
+        <v>1.7532000000000001</v>
+      </c>
+      <c r="G2321">
+        <v>198449649</v>
+      </c>
+      <c r="H2321" s="3">
+        <v>310909000000</v>
+      </c>
+      <c r="I2321">
+        <f t="shared" si="91"/>
+        <v>2319</v>
+      </c>
+      <c r="J2321">
+        <f>SUM($F$3:F2321)/I2321</f>
+        <v>1.188848292367398</v>
+      </c>
+      <c r="K2321">
+        <f t="shared" si="95"/>
+        <v>1.8560473999999991</v>
+      </c>
+    </row>
+    <row r="2322" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2322" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B2322">
+        <v>1753.84</v>
+      </c>
+      <c r="C2322">
+        <v>1754.37</v>
+      </c>
+      <c r="D2322">
+        <v>1703.38</v>
+      </c>
+      <c r="E2322">
+        <v>1712.71</v>
+      </c>
+      <c r="F2322">
+        <f t="shared" si="94"/>
+        <v>1.71271</v>
+      </c>
+      <c r="G2322">
+        <v>211091657</v>
+      </c>
+      <c r="H2322" s="3">
+        <v>328176000000</v>
+      </c>
+      <c r="I2322">
+        <f t="shared" si="91"/>
+        <v>2320</v>
+      </c>
+      <c r="J2322">
+        <f>SUM($F$3:F2322)/I2322</f>
+        <v>1.1890740948275844</v>
+      </c>
+      <c r="K2322">
+        <f t="shared" si="95"/>
+        <v>1.8553893199999993</v>
+      </c>
+    </row>
+    <row r="2323" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2323" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B2323">
+        <v>1708.55</v>
+      </c>
+      <c r="C2323">
+        <v>1740.44</v>
+      </c>
+      <c r="D2323">
+        <v>1706.24</v>
+      </c>
+      <c r="E2323">
+        <v>1731.4</v>
+      </c>
+      <c r="F2323">
+        <f t="shared" si="94"/>
+        <v>1.7314000000000001</v>
+      </c>
+      <c r="G2323">
+        <v>185990876</v>
+      </c>
+      <c r="H2323" s="3">
+        <v>277119000000</v>
+      </c>
+      <c r="I2323">
+        <f t="shared" si="91"/>
+        <v>2321</v>
+      </c>
+      <c r="J2323">
+        <f>SUM($F$3:F2323)/I2323</f>
+        <v>1.1893077552778957</v>
+      </c>
+      <c r="K2323">
+        <f t="shared" si="95"/>
+        <v>1.854694719999999</v>
+      </c>
+    </row>
+    <row r="2324" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2324" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B2324">
+        <v>1737.18</v>
+      </c>
+      <c r="C2324">
+        <v>1738.13</v>
+      </c>
+      <c r="D2324">
+        <v>1719.46</v>
+      </c>
+      <c r="E2324">
+        <v>1723.01</v>
+      </c>
+      <c r="F2324">
+        <f t="shared" si="94"/>
+        <v>1.7230099999999999</v>
+      </c>
+      <c r="G2324">
+        <v>181620786</v>
+      </c>
+      <c r="H2324" s="3">
+        <v>283499000000</v>
+      </c>
+      <c r="I2324">
+        <f t="shared" si="91"/>
+        <v>2322</v>
+      </c>
+      <c r="J2324">
+        <f>SUM($F$3:F2324)/I2324</f>
+        <v>1.1895376012058554</v>
+      </c>
+      <c r="K2324">
+        <f t="shared" si="95"/>
+        <v>1.8539441999999993</v>
       </c>
     </row>
   </sheetData>
